--- a/artfynd/A 34166-2023 artfynd.xlsx
+++ b/artfynd/A 34166-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34166-2023 artfynd.xlsx
+++ b/artfynd/A 34166-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>70845195</v>
+        <v>126404318</v>
       </c>
       <c r="B2" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,24 +704,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lidsäter, Vg</t>
+          <t>Rya, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>356556.2353212574</v>
+        <v>356556</v>
       </c>
       <c r="R2" t="n">
-        <v>6383072.978329462</v>
+        <v>6383073</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,27 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2007-11-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-06-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2007-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-06-18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ek</t>
+          <t>Hasselmusinventering Boris Berglund 2007, Inrapporterad av Marks kommun</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Boris Berglund</t>
+          <t>Via Jenny Pleym</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 34166-2023 artfynd.xlsx
+++ b/artfynd/A 34166-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126404318</v>
       </c>
       <c r="B2" t="n">
-        <v>56324</v>
+        <v>56325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34166-2023 artfynd.xlsx
+++ b/artfynd/A 34166-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>126404318</v>
       </c>
       <c r="B2" t="n">
-        <v>56325</v>
+        <v>56614</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -774,6 +774,125 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6859787</v>
+      </c>
+      <c r="B3" t="n">
+        <v>107720</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>223653</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig hässleklocka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Campanula latifolia var. latifolia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lidsäter, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>356574</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6383060</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hyssna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2013-07-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2013-07-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Efter väg</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lennart Walldén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lennart Walldén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
